--- a/paper/数字一致性审计.xlsx
+++ b/paper/数字一致性审计.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="numbers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,264 +413,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>number_name</t>
+          <t>item</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>paper_value</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>found_in_paper</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>match</t>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>report_count</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+          <t>stock_guidance_novelty_beta</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7466450326474896</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+          <t>output/results/stock_volatility_main.json</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dictionary_entries</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+          <t>stock_guidance_novelty_p</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.02576008023627007</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+          <t>output/results/stock_volatility_main.json</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>annotation_rows</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+          <t>stock_post_2019_total_effect</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.290985416460928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+          <t>output/results/stock_volatility_main.json</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>primary_n</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>bond_unexpected_tone_beta</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9541998492202118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
+          <t>output/results/yield_curve_results.csv</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>primary_beta</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-1.081</t>
-        </is>
+          <t>egarch_x_novelty_coef</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0955076786677384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>primary_se</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.912</t>
-        </is>
+          <t>egarch_x_formal_lr_p</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1887370910306666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>primary_p</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.572</t>
-        </is>
+          <t>egarch_x_variance_change_pct</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10.02172702043578</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>primary_ci_low</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>-4.828</t>
-        </is>
+          <t>power_max</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9325</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
+          <t>output/diagnostics/market_power_analysis.csv</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>primary_ci_high</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.667</t>
-        </is>
+          <t>cross_fitted_policy_relevant_coef</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4744212511114123</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
+          <t>output/results/cross_fitted_bond_exploration.csv</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>permutation_p</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.604</t>
-        </is>
+          <t>manual_validation_rows</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>output/results/primary/PRIMARY_RESULT_LOCK.json or diagnostics gates</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
+          <t>data/validation/manual_sentence_annotation_filled.xlsx</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/paper/数字一致性审计.xlsx
+++ b/paper/数字一致性审计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0955076786677384</v>
+        <v>0.09444690550353113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1887370910306666</v>
+        <v>0.1887716020499765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.02172702043578</v>
+        <v>9.905080803459022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -571,13 +571,73 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>svc_sentiment_cv_accuracy</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>svc_policy_stance_cv_accuracy</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.8583333333333333</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>svc_policy_direction_cv_accuracy</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>svc_topic_cv_macro_f1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3329096913900582</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>manual_validation_rows</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B15" t="n">
         <v>240</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>data/validation/manual_sentence_annotation_filled.xlsx</t>
         </is>

--- a/paper/数字一致性审计.xlsx
+++ b/paper/数字一致性审计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,161 +466,161 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stock_post_2019_total_effect</t>
+          <t>stock_guidance_novelty_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.290985416460928</v>
+        <v>0.1631866708367444</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>output/results/stock_volatility_main.json</t>
+          <t>data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bond_unexpected_tone_beta</t>
+          <t>stock_guidance_novelty_one_sd_effect_percent</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9541998492202118</v>
+        <v>12.95761989209812</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>output/results/yield_curve_results.csv</t>
+          <t>output/results/stock_volatility_main.json + data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>egarch_x_novelty_coef</t>
+          <t>stock_guidance_novelty_one_unit_effect_percent</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09444690550353113</v>
+        <v>110.9909451629524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>output/results/daily_egarch_x_results.json</t>
+          <t>output/results/stock_volatility_main.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>egarch_x_formal_lr_p</t>
+          <t>stock_post_2019_total_effect</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1887716020499765</v>
+        <v>0.290985416460928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>output/results/daily_egarch_x_results.json</t>
+          <t>output/results/stock_volatility_main.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>egarch_x_variance_change_pct</t>
+          <t>bond_unexpected_tone_beta</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.905080803459022</v>
+        <v>0.9541998492202118</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>output/results/daily_egarch_x_results.json</t>
+          <t>output/results/yield_curve_results.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>power_max</t>
+          <t>egarch_x_novelty_coef</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9325</v>
+        <v>0.09444690550353113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>output/diagnostics/market_power_analysis.csv</t>
+          <t>output/results/daily_egarch_x_results.json</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cross_fitted_policy_relevant_coef</t>
+          <t>egarch_x_formal_lr_p</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4744212511114123</v>
+        <v>0.1887716020499765</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>output/results/cross_fitted_bond_exploration.csv</t>
+          <t>output/results/daily_egarch_x_results.json</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svc_sentiment_cv_accuracy</t>
+          <t>egarch_x_variance_change_pct</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8958333333333334</v>
+        <v>9.905080803459022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/results/daily_egarch_x_results.json</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>svc_policy_stance_cv_accuracy</t>
+          <t>power_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8583333333333333</v>
+        <v>0.9325</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/diagnostics/market_power_analysis.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>svc_policy_direction_cv_accuracy</t>
+          <t>cross_fitted_policy_relevant_coef</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.4744212511114123</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/results/cross_fitted_bond_exploration.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>svc_topic_cv_macro_f1</t>
+          <t>svc_sentiment_cv_accuracy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3329096913900582</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -631,13 +631,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>svc_policy_stance_cv_accuracy</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8583333333333333</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>svc_policy_direction_cv_accuracy</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>svc_topic_cv_macro_f1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3329096913900582</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>manual_validation_rows</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B18" t="n">
         <v>240</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>data/validation/manual_sentence_annotation_filled.xlsx</t>
         </is>

--- a/paper/数字一致性审计.xlsx
+++ b/paper/数字一致性审计.xlsx
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09444690550353113</v>
+        <v>0.0955076786677384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1887716020499765</v>
+        <v>0.1887370910306666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.905080803459022</v>
+        <v>10.02172702043578</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/paper/数字一致性审计.xlsx
+++ b/paper/数字一致性审计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,255 +436,634 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stock_guidance_novelty_beta</t>
+          <t>formal_reports</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7466450326474896</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>output/results/stock_volatility_main.json</t>
+          <t>data/processed/refactor_text_features.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stock_guidance_novelty_p</t>
+          <t>manual_sentences</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02576008023627007</v>
+        <v>240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>output/results/stock_volatility_main.json</t>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stock_guidance_novelty_std</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.1631866708367444</v>
+          <t>report_start</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2006Q1</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>data/processed/refactor_stock_event_panel.csv</t>
+          <t>data/processed/refactor_text_features.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stock_guidance_novelty_one_sd_effect_percent</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>12.95761989209812</v>
+          <t>report_end</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>output/results/stock_volatility_main.json + data/processed/refactor_stock_event_panel.csv</t>
+          <t>data/processed/refactor_text_features.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stock_guidance_novelty_one_unit_effect_percent</t>
+          <t>stock_n</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.9909451629524</v>
+        <v>79</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>output/results/stock_volatility_main.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stock_post_2019_total_effect</t>
+          <t>stock_beta</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.290985416460928</v>
+        <v>0.7466450326474896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>output/results/stock_volatility_main.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bond_unexpected_tone_beta</t>
+          <t>stock_se</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9541998492202118</v>
+        <v>0.3348469773235418</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>output/results/yield_curve_results.csv</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>egarch_x_novelty_coef</t>
+          <t>stock_p</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0955076786677384</v>
+        <v>0.02576008023627007</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>output/results/daily_egarch_x_results.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>egarch_x_formal_lr_p</t>
+          <t>stock_r2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1887370910306666</v>
+        <v>0.4547018196962095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>output/results/daily_egarch_x_results.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>egarch_x_variance_change_pct</t>
+          <t>stock_interaction</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.02172702043578</v>
+        <v>-0.4556596161865616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>output/results/daily_egarch_x_results.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>power_max</t>
+          <t>stock_interaction_p</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9325</v>
+        <v>0.5011016272718196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>output/diagnostics/market_power_analysis.csv</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cross_fitted_policy_relevant_coef</t>
+          <t>stock_total</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4744212511114123</v>
+        <v>0.290985416460928</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>output/results/cross_fitted_bond_exploration.csv</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>svc_sentiment_cv_accuracy</t>
+          <t>stock_total_p</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.6527022742493203</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>svc_policy_stance_cv_accuracy</t>
+          <t>guidance_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8583333333333333</v>
+        <v>0.1631866708367444</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>svc_policy_direction_cv_accuracy</t>
+          <t>stock_one_sd_pct</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7878787878787878</v>
+        <v>12.95761989209812</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/results/stock_volatility_main.json; data/processed/refactor_stock_event_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>svc_topic_cv_macro_f1</t>
+          <t>egarch_n</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3329096913900582</v>
+        <v>4888</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>output/results/text_model_evaluation.json</t>
+          <t>output/results/daily_egarch_x_results.json</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>manual_validation_rows</t>
+          <t>egarch_events</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>data/validation/manual_sentence_annotation_filled.xlsx</t>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>egarch_novelty_coef</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.09444690550353113</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>egarch_lr_p</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1887716020499765</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>egarch_perm_p</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>egarch_vol_pct</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.835624099567903</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>output/results/daily_egarch_x_results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>power_current</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>output/diagnostics/market_power_analysis.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>power_120</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>output/diagnostics/market_power_analysis.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>power_160</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9325</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>output/diagnostics/market_power_analysis.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bond_beta</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.9541998492202118</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>output/results/yield_curve_results.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bond_se</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.185767495594914</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>output/results/yield_curve_results.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bond_p</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.4209866154117416</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>output/results/yield_curve_results.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bond_total</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.6080078448339598</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>output/results/yield_curve_results.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bond_total_p</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.7239214111033228</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>output/results/yield_curve_results.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_coef</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.4744212511114123</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>output/results/cross_fitted_bond_exploration.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_p</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.9079143463662924</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>output/results/cross_fitted_bond_exploration.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_total</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.1124215906650885</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>output/results/cross_fitted_bond_exploration.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_total_p</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.9851898878347952</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>output/results/cross_fitted_bond_exploration.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>svc_sentiment_acc</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>svc_sentiment_f1</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.7992858873758079</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>svc_stance_acc</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.8583333333333333</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>svc_stance_f1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.6804294279695349</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>svc_direction_acc</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>svc_direction_f1</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.730088544244624</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>lexicon_sentiment_acc</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.2958333333333333</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>lexicon_stance_acc</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>lexicon_direction_acc</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>output/results/text_model_evaluation.json; output/diagnostics/text_validation_metrics.xlsx</t>
         </is>
       </c>
     </row>

--- a/paper/数字一致性审计.xlsx
+++ b/paper/数字一致性审计.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1631866708367444</v>
+        <v>0.1631866708367445</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2958</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5303030303030303</v>
+        <v>0.5303</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
